--- a/工作分配.xlsx
+++ b/工作分配.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\AIPE03第一組\kanbanBoard-everyone_ignore-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{884EAC8F-6614-4683-B0D8-32B89A9A64B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{156744BE-26F2-4C53-8E78-EFA0D4DAEB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6768" yWindow="12852" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-6768" yWindow="12852" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作分配總表" sheetId="1" r:id="rId1"/>
@@ -4685,23 +4685,6 @@
         <charset val="136"/>
       </rPr>
       <t>進度追蹤</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>架構與技術細節掌握</t>
     </r>
     <r>
       <rPr>
@@ -5107,37 +5090,6 @@
   </cellStyleXfs>
   <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5315,6 +5267,37 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5596,1251 +5579,1251 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
+      <c r="L1" s="68"/>
     </row>
     <row r="2" spans="1:13" ht="19.5" customHeight="1">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
+      <c r="B2" s="69"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="69"/>
+      <c r="K2" s="69"/>
+      <c r="L2" s="69"/>
     </row>
     <row r="3" spans="1:13" ht="24" customHeight="1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="12" t="s">
+      <c r="J3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="12" t="s">
+      <c r="K3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="L3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="7">
         <v>1</v>
       </c>
-      <c r="G4" s="19" t="s">
+      <c r="G4" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="7">
         <v>1</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="7">
         <v>15</v>
       </c>
-      <c r="J4" s="18">
+      <c r="J4" s="7">
         <f t="shared" ref="J4:J31" si="0">I4-H4+1</f>
         <v>15</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="20" t="s">
+      <c r="L4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="21" t="s">
+      <c r="M4" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="115.5" customHeight="1">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="7">
         <v>2</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="7">
         <v>1</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="7">
         <v>3</v>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K5" s="16" t="s">
+      <c r="K5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="16" t="s">
+      <c r="L5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="M5" s="25" t="s">
+      <c r="M5" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="7">
         <v>1</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="G6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="7">
         <v>2</v>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="7">
         <v>4</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="20" t="s">
+      <c r="L6" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="M6" s="25" t="s">
+      <c r="M6" s="14" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="102" customHeight="1">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="7">
         <v>2</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="7">
         <v>2</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="7">
         <v>5</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="20" t="s">
+      <c r="L7" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="14" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="7">
         <v>3</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="7">
         <v>3</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="7">
         <v>5</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="M8" s="21" t="s">
+      <c r="M8" s="10" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="7">
         <v>1</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="7">
         <v>1</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="7">
         <v>2</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="20" t="s">
+      <c r="L9" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="21" t="s">
+      <c r="M9" s="10" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="7">
         <v>1</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="7">
         <v>2</v>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="7">
         <v>4</v>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="20" t="s">
+      <c r="L10" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="M10" s="10" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="7">
         <v>7</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="7">
         <v>4</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="7">
         <v>6</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="20" t="s">
+      <c r="L11" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="M11" s="21" t="s">
+      <c r="M11" s="10" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="7">
         <v>1</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="7">
         <v>1</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="7">
         <v>3</v>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="L12" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="21" t="s">
+      <c r="M12" s="10" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="7">
         <v>1</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="G13" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="7">
         <v>1</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="7">
         <v>2</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L13" s="20" t="s">
+      <c r="L13" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="M13" s="21" t="s">
+      <c r="M13" s="10" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="7">
         <v>1</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="7">
         <v>6</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="7">
         <v>9</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K14" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="L14" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="M14" s="21" t="s">
+      <c r="M14" s="10" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="F15" s="18">
+      <c r="F15" s="7">
         <v>2</v>
       </c>
-      <c r="G15" s="19" t="s">
+      <c r="G15" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="7">
         <v>6</v>
       </c>
-      <c r="I15" s="18">
+      <c r="I15" s="7">
         <v>7</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="K15" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="L15" s="20" t="s">
+      <c r="L15" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="M15" s="21" t="s">
+      <c r="M15" s="10" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="7">
         <v>1</v>
       </c>
-      <c r="G16" s="19" t="s">
+      <c r="G16" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="7">
         <v>7</v>
       </c>
-      <c r="I16" s="18">
+      <c r="I16" s="7">
         <v>10</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K16" s="16" t="s">
+      <c r="K16" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="L16" s="20" t="s">
+      <c r="L16" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="M16" s="21" t="s">
+      <c r="M16" s="10" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="7">
         <v>1</v>
       </c>
-      <c r="G17" s="19" t="s">
+      <c r="G17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="7">
         <v>1</v>
       </c>
-      <c r="I17" s="18">
+      <c r="I17" s="7">
         <v>5</v>
       </c>
-      <c r="J17" s="18">
+      <c r="J17" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="K17" s="16" t="s">
+      <c r="K17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L17" s="20" t="s">
+      <c r="L17" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="M17" s="21" t="s">
+      <c r="M17" s="10" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="32" t="s">
+      <c r="B18" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="E18" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="7">
         <v>1</v>
       </c>
-      <c r="G18" s="30" t="s">
+      <c r="G18" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="7">
         <v>8</v>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="7">
         <v>10</v>
       </c>
-      <c r="J18" s="18">
+      <c r="J18" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K18" s="16" t="s">
+      <c r="K18" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="L18" s="20" t="s">
+      <c r="L18" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="M18" s="21" t="s">
+      <c r="M18" s="10" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="7">
         <v>2</v>
       </c>
-      <c r="G19" s="19" t="s">
+      <c r="G19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="18">
+      <c r="H19" s="7">
         <v>6</v>
       </c>
-      <c r="I19" s="18">
+      <c r="I19" s="7">
         <v>9</v>
       </c>
-      <c r="J19" s="18">
+      <c r="J19" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K19" s="16" t="s">
+      <c r="K19" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="L19" s="16" t="s">
+      <c r="L19" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="M19" s="21" t="s">
+      <c r="M19" s="10" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="E20" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="7">
         <v>1</v>
       </c>
-      <c r="G20" s="19" t="s">
+      <c r="G20" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="7">
         <v>3</v>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="7">
         <v>6</v>
       </c>
-      <c r="J20" s="18">
+      <c r="J20" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K20" s="16" t="s">
+      <c r="K20" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="L20" s="16" t="s">
+      <c r="L20" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="M20" s="21" t="s">
+      <c r="M20" s="10" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="7">
         <v>3</v>
       </c>
-      <c r="G21" s="19" t="s">
+      <c r="G21" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="7">
         <v>8</v>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="7">
         <v>11</v>
       </c>
-      <c r="J21" s="18">
+      <c r="J21" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K21" s="16" t="s">
+      <c r="K21" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="L21" s="16" t="s">
+      <c r="L21" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="M21" s="21" t="s">
+      <c r="M21" s="10" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="D22" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="E22" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="18">
+      <c r="F22" s="7">
         <v>1</v>
       </c>
-      <c r="G22" s="19" t="s">
+      <c r="G22" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H22" s="18">
+      <c r="H22" s="7">
         <v>6</v>
       </c>
-      <c r="I22" s="18">
+      <c r="I22" s="7">
         <v>8</v>
       </c>
-      <c r="J22" s="18">
+      <c r="J22" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K22" s="16" t="s">
+      <c r="K22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="L22" s="20" t="s">
+      <c r="L22" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="M22" s="21" t="s">
+      <c r="M22" s="10" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B23" s="32" t="s">
+      <c r="B23" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E23" s="17" t="s">
+      <c r="E23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="18">
+      <c r="F23" s="7">
         <v>1</v>
       </c>
-      <c r="G23" s="19" t="s">
+      <c r="G23" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="18">
+      <c r="H23" s="7">
         <v>8</v>
       </c>
-      <c r="I23" s="18">
+      <c r="I23" s="7">
         <v>10</v>
       </c>
-      <c r="J23" s="18">
+      <c r="J23" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K23" s="16" t="s">
+      <c r="K23" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="L23" s="20" t="s">
+      <c r="L23" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="M23" s="25" t="s">
+      <c r="M23" s="14" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F24" s="18">
+      <c r="F24" s="7">
         <v>6</v>
       </c>
-      <c r="G24" s="19" t="s">
+      <c r="G24" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="7">
         <v>11</v>
       </c>
-      <c r="I24" s="18">
+      <c r="I24" s="7">
         <v>13</v>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K24" s="16" t="s">
+      <c r="K24" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="L24" s="20" t="s">
+      <c r="L24" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="M24" s="21" t="s">
+      <c r="M24" s="10" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="87.75" customHeight="1">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="7">
         <v>2</v>
       </c>
-      <c r="G25" s="19" t="s">
+      <c r="G25" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="18">
+      <c r="H25" s="7">
         <v>11</v>
       </c>
-      <c r="I25" s="18">
+      <c r="I25" s="7">
         <v>14</v>
       </c>
-      <c r="J25" s="18">
+      <c r="J25" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K25" s="16" t="s">
+      <c r="K25" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="L25" s="20" t="s">
+      <c r="L25" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="M25" s="21" t="s">
+      <c r="M25" s="10" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="60" customHeight="1">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="F26" s="18">
+      <c r="F26" s="7">
         <v>2</v>
       </c>
-      <c r="G26" s="19" t="s">
+      <c r="G26" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H26" s="18">
+      <c r="H26" s="7">
         <v>11</v>
       </c>
-      <c r="I26" s="18">
+      <c r="I26" s="7">
         <v>14</v>
       </c>
-      <c r="J26" s="18">
+      <c r="J26" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="K26" s="16" t="s">
+      <c r="K26" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="L26" s="20" t="s">
+      <c r="L26" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="M26" s="21" t="s">
+      <c r="M26" s="10" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="34" t="s">
+      <c r="B27" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C27" s="35" t="s">
+      <c r="C27" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="D27" s="20" t="s">
+      <c r="D27" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="F27" s="18">
+      <c r="F27" s="7">
         <v>2</v>
       </c>
-      <c r="G27" s="30" t="s">
+      <c r="G27" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H27" s="18">
+      <c r="H27" s="7">
         <v>11</v>
       </c>
-      <c r="I27" s="18">
+      <c r="I27" s="7">
         <v>13</v>
       </c>
-      <c r="J27" s="18">
+      <c r="J27" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K27" s="16" t="s">
+      <c r="K27" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="L27" s="16" t="s">
+      <c r="L27" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="M27" s="21" t="s">
+      <c r="M27" s="10" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="73.5" customHeight="1">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="7">
         <v>1</v>
       </c>
-      <c r="G28" s="30" t="s">
+      <c r="G28" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="7">
         <v>12</v>
       </c>
-      <c r="I28" s="18">
+      <c r="I28" s="7">
         <v>14</v>
       </c>
-      <c r="J28" s="18">
+      <c r="J28" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="K28" s="16" t="s">
+      <c r="K28" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="L28" s="20" t="s">
+      <c r="L28" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="M28" s="21" t="s">
+      <c r="M28" s="10" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="60" customHeight="1">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="D29" s="20" t="s">
+      <c r="D29" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="F29" s="18">
+      <c r="F29" s="7">
         <v>3</v>
       </c>
-      <c r="G29" s="19" t="s">
+      <c r="G29" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H29" s="18">
+      <c r="H29" s="7">
         <v>13</v>
       </c>
-      <c r="I29" s="18">
+      <c r="I29" s="7">
         <v>14</v>
       </c>
-      <c r="J29" s="18">
+      <c r="J29" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K29" s="16" t="s">
+      <c r="K29" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="L29" s="20" t="s">
+      <c r="L29" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="M29" s="21" t="s">
+      <c r="M29" s="10" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="60" customHeight="1">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="D30" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E30" s="28" t="s">
+      <c r="E30" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F30" s="18">
+      <c r="F30" s="7">
         <v>7</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="G30" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H30" s="18">
+      <c r="H30" s="7">
         <v>14</v>
       </c>
-      <c r="I30" s="18">
+      <c r="I30" s="7">
         <v>15</v>
       </c>
-      <c r="J30" s="18">
+      <c r="J30" s="7">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K30" s="16" t="s">
+      <c r="K30" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="L30" s="16" t="s">
+      <c r="L30" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="M30" s="21" t="s">
+      <c r="M30" s="10" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="45.75" customHeight="1">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="25" t="s">
         <v>157</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E31" s="28" t="s">
+      <c r="E31" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="F31" s="18">
+      <c r="F31" s="7">
         <v>7</v>
       </c>
-      <c r="G31" s="30" t="s">
+      <c r="G31" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="H31" s="18">
+      <c r="H31" s="7">
         <v>15</v>
       </c>
-      <c r="I31" s="18">
+      <c r="I31" s="7">
         <v>15</v>
       </c>
-      <c r="J31" s="18">
+      <c r="J31" s="7">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="K31" s="16" t="s">
+      <c r="K31" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="16" t="s">
+      <c r="L31" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="M31" s="21" t="s">
+      <c r="M31" s="10" t="s">
         <v>164</v>
       </c>
     </row>
@@ -6868,966 +6851,966 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="25.5" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="67" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="70" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7" t="s">
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="6" t="s">
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="72" t="s">
         <v>77</v>
       </c>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="5" t="s">
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="72"/>
+      <c r="N2" s="72"/>
+      <c r="O2" s="73" t="s">
         <v>123</v>
       </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
+      <c r="P2" s="73"/>
+      <c r="Q2" s="73"/>
+      <c r="R2" s="73"/>
+      <c r="S2" s="73"/>
     </row>
     <row r="3" spans="1:19" ht="16.5" customHeight="1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="J3" s="37" t="s">
+      <c r="J3" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="K3" s="37" t="s">
+      <c r="K3" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="L3" s="37" t="s">
+      <c r="L3" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="M3" s="37" t="s">
+      <c r="M3" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="N3" s="37" t="s">
+      <c r="N3" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="O3" s="37" t="s">
+      <c r="O3" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="P3" s="37" t="s">
+      <c r="P3" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="Q3" s="37" t="s">
+      <c r="Q3" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="R3" s="37" t="s">
+      <c r="R3" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="S3" s="37" t="s">
+      <c r="S3" s="26" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="26.25" customHeight="1">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="42"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="42"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
     </row>
     <row r="5" spans="1:19" ht="26.25" customHeight="1">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="38" t="s">
+      <c r="D5" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="45" t="s">
+      <c r="E5" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="47"/>
-      <c r="J5" s="47"/>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="47"/>
-      <c r="P5" s="47"/>
-      <c r="Q5" s="47"/>
-      <c r="R5" s="47"/>
-      <c r="S5" s="47"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
     </row>
     <row r="6" spans="1:19" ht="15" customHeight="1">
-      <c r="A6" s="38" t="s">
+      <c r="A6" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="39" t="s">
+      <c r="B6" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="E6" s="47"/>
-      <c r="F6" s="45" t="s">
+      <c r="E6" s="36"/>
+      <c r="F6" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="47"/>
-      <c r="P6" s="47"/>
-      <c r="Q6" s="47"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
     </row>
     <row r="7" spans="1:19" ht="26.25" customHeight="1">
-      <c r="A7" s="38" t="s">
+      <c r="A7" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="38" t="s">
+      <c r="D7" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="47"/>
-      <c r="F7" s="45" t="s">
+      <c r="E7" s="36"/>
+      <c r="F7" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="47"/>
-      <c r="K7" s="47"/>
-      <c r="L7" s="47"/>
-      <c r="M7" s="47"/>
-      <c r="N7" s="47"/>
-      <c r="O7" s="47"/>
-      <c r="P7" s="47"/>
-      <c r="Q7" s="47"/>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
+      <c r="S7" s="36"/>
     </row>
     <row r="8" spans="1:19" ht="15" customHeight="1">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="38" t="s">
+      <c r="D8" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="G8" s="45" t="s">
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="47"/>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-      <c r="M8" s="47"/>
-      <c r="N8" s="47"/>
-      <c r="O8" s="47"/>
-      <c r="P8" s="47"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="36"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="36"/>
+      <c r="S8" s="36"/>
     </row>
     <row r="9" spans="1:19" ht="15" customHeight="1">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="43" t="s">
+      <c r="B9" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="38" t="s">
+      <c r="D9" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="49" t="s">
+      <c r="E9" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="50"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="47"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="47"/>
-      <c r="N9" s="47"/>
-      <c r="O9" s="47"/>
-      <c r="P9" s="47"/>
-      <c r="Q9" s="47"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="36"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="36"/>
+      <c r="S9" s="36"/>
     </row>
     <row r="10" spans="1:19" ht="15" customHeight="1">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D10" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="47"/>
-      <c r="F10" s="49" t="s">
+      <c r="E10" s="36"/>
+      <c r="F10" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="47"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="47"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="47"/>
-      <c r="Q10" s="47"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="47"/>
+      <c r="G10" s="39"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
+      <c r="S10" s="36"/>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="D11" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E11" s="47"/>
-      <c r="F11" s="47"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="53" t="s">
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="42" t="s">
         <v>60</v>
       </c>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="47"/>
-      <c r="L11" s="47"/>
-      <c r="M11" s="47"/>
-      <c r="N11" s="47"/>
-      <c r="O11" s="47"/>
-      <c r="P11" s="47"/>
-      <c r="Q11" s="47"/>
-      <c r="R11" s="47"/>
-      <c r="S11" s="47"/>
+      <c r="I11" s="43"/>
+      <c r="J11" s="43"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="36"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
+      <c r="S11" s="36"/>
     </row>
     <row r="12" spans="1:19" ht="15" customHeight="1">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D12" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="47"/>
-      <c r="L12" s="47"/>
-      <c r="M12" s="47"/>
-      <c r="N12" s="47"/>
-      <c r="O12" s="47"/>
-      <c r="P12" s="47"/>
-      <c r="Q12" s="47"/>
-      <c r="R12" s="47"/>
-      <c r="S12" s="47"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="36"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="36"/>
+      <c r="S12" s="36"/>
     </row>
     <row r="13" spans="1:19" ht="15" customHeight="1">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="E13" s="59" t="s">
+      <c r="E13" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="47"/>
-      <c r="L13" s="47"/>
-      <c r="M13" s="47"/>
-      <c r="N13" s="47"/>
-      <c r="O13" s="47"/>
-      <c r="P13" s="47"/>
-      <c r="Q13" s="47"/>
-      <c r="R13" s="47"/>
-      <c r="S13" s="47"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="36"/>
+      <c r="S13" s="36"/>
     </row>
     <row r="14" spans="1:19" ht="26.25" customHeight="1">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="38" t="s">
+      <c r="D14" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="49" t="s">
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="38" t="s">
         <v>49</v>
       </c>
-      <c r="K14" s="50"/>
-      <c r="L14" s="50"/>
-      <c r="M14" s="50"/>
-      <c r="N14" s="47"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="39"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="36"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="36"/>
+      <c r="S14" s="36"/>
     </row>
     <row r="15" spans="1:19" ht="15" customHeight="1">
-      <c r="A15" s="38" t="s">
+      <c r="A15" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="38" t="s">
+      <c r="D15" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="62" t="s">
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="K15" s="54"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="47"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="36"/>
+      <c r="S15" s="36"/>
     </row>
     <row r="16" spans="1:19" ht="15" customHeight="1">
-      <c r="A16" s="38" t="s">
+      <c r="A16" s="27" t="s">
         <v>86</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="47"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="62" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="51" t="s">
         <v>83</v>
       </c>
-      <c r="L16" s="54"/>
-      <c r="M16" s="54"/>
-      <c r="N16" s="54"/>
-      <c r="O16" s="47"/>
-      <c r="P16" s="47"/>
-      <c r="Q16" s="47"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47"/>
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
+      <c r="S16" s="36"/>
     </row>
     <row r="17" spans="1:19" ht="26.25" customHeight="1">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="C17" s="63" t="s">
+      <c r="C17" s="52" t="s">
         <v>189</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="E17" s="64" t="s">
+      <c r="E17" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="47"/>
-      <c r="L17" s="47"/>
-      <c r="M17" s="47"/>
-      <c r="N17" s="47"/>
-      <c r="O17" s="47"/>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="47"/>
-      <c r="R17" s="47"/>
-      <c r="S17" s="47"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
+      <c r="I17" s="54"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="36"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="36"/>
+      <c r="S17" s="36"/>
     </row>
     <row r="18" spans="1:19" ht="15" customHeight="1">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="C18" s="63" t="s">
+      <c r="C18" s="52" t="s">
         <v>189</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="27" t="s">
         <v>93</v>
       </c>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
-      <c r="G18" s="47"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="47"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="47"/>
-      <c r="L18" s="64" t="s">
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="36"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="53" t="s">
         <v>93</v>
       </c>
-      <c r="M18" s="65"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="47"/>
-      <c r="P18" s="47"/>
-      <c r="Q18" s="47"/>
-      <c r="R18" s="47"/>
-      <c r="S18" s="47"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="36"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="36"/>
+      <c r="S18" s="36"/>
     </row>
     <row r="19" spans="1:19" ht="15" customHeight="1">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="27" t="s">
         <v>191</v>
       </c>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="59" t="s">
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="K19" s="60"/>
-      <c r="L19" s="60"/>
-      <c r="M19" s="60"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="47"/>
-      <c r="Q19" s="47"/>
-      <c r="R19" s="47"/>
-      <c r="S19" s="47"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="36"/>
+      <c r="S19" s="36"/>
     </row>
     <row r="20" spans="1:19" ht="15" customHeight="1">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="59" t="s">
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="60"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="59"/>
-      <c r="K20" s="47"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
-      <c r="N20" s="47"/>
-      <c r="O20" s="47"/>
-      <c r="P20" s="47"/>
-      <c r="Q20" s="47"/>
-      <c r="R20" s="47"/>
-      <c r="S20" s="47"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="36"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="36"/>
+      <c r="S20" s="36"/>
     </row>
     <row r="21" spans="1:19" ht="26.25" customHeight="1">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="47" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="D21" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="47"/>
-      <c r="G21" s="47"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="47"/>
-      <c r="J21" s="47"/>
-      <c r="K21" s="47"/>
-      <c r="L21" s="59" t="s">
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="M21" s="60"/>
-      <c r="N21" s="60"/>
-      <c r="O21" s="60"/>
-      <c r="P21" s="47"/>
-      <c r="Q21" s="47"/>
-      <c r="R21" s="47"/>
-      <c r="S21" s="47"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="49"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="36"/>
+      <c r="S21" s="36"/>
     </row>
     <row r="22" spans="1:19" ht="15" customHeight="1">
-      <c r="A22" s="38" t="s">
+      <c r="A22" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="B22" s="43" t="s">
+      <c r="B22" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="C22" s="55" t="s">
+      <c r="C22" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="47"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="47"/>
-      <c r="H22" s="47"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="56" t="s">
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="45" t="s">
         <v>66</v>
       </c>
-      <c r="K22" s="57"/>
-      <c r="L22" s="57"/>
-      <c r="M22" s="47"/>
-      <c r="N22" s="47"/>
-      <c r="O22" s="47"/>
-      <c r="P22" s="47"/>
-      <c r="Q22" s="47"/>
-      <c r="R22" s="47"/>
-      <c r="S22" s="47"/>
+      <c r="K22" s="46"/>
+      <c r="L22" s="46"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="36"/>
+      <c r="S22" s="36"/>
     </row>
     <row r="23" spans="1:19" ht="15" customHeight="1">
-      <c r="A23" s="38" t="s">
+      <c r="A23" s="27" t="s">
         <v>117</v>
       </c>
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="D23" s="38" t="s">
+      <c r="D23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="E23" s="47"/>
-      <c r="F23" s="47"/>
-      <c r="G23" s="47"/>
-      <c r="H23" s="47"/>
-      <c r="I23" s="47"/>
-      <c r="J23" s="47"/>
-      <c r="K23" s="47"/>
-      <c r="L23" s="45" t="s">
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="36"/>
+      <c r="J23" s="36"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="M23" s="46"/>
-      <c r="N23" s="46"/>
-      <c r="O23" s="47"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="47"/>
-      <c r="S23" s="47"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="36"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="36"/>
+      <c r="S23" s="36"/>
     </row>
     <row r="24" spans="1:19" ht="15" customHeight="1">
-      <c r="A24" s="38" t="s">
+      <c r="A24" s="27" t="s">
         <v>122</v>
       </c>
-      <c r="B24" s="43" t="s">
+      <c r="B24" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="27" t="s">
         <v>194</v>
       </c>
-      <c r="E24" s="47"/>
-      <c r="F24" s="47"/>
-      <c r="G24" s="47"/>
-      <c r="H24" s="47"/>
-      <c r="I24" s="47"/>
-      <c r="J24" s="47"/>
-      <c r="K24" s="47"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
-      <c r="N24" s="47"/>
-      <c r="O24" s="66" t="s">
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+      <c r="J24" s="36"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="36"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="47"/>
-      <c r="S24" s="47"/>
+      <c r="P24" s="31"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="36"/>
+      <c r="S24" s="36"/>
     </row>
     <row r="25" spans="1:19" ht="26.25" customHeight="1">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="D25" s="27" t="s">
         <v>130</v>
       </c>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="47"/>
-      <c r="J25" s="47"/>
-      <c r="K25" s="47"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
-      <c r="N25" s="47"/>
-      <c r="O25" s="41" t="s">
+      <c r="E25" s="36"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="36"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="36"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="42"/>
-      <c r="S25" s="47"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="36"/>
     </row>
     <row r="26" spans="1:19" ht="15" customHeight="1">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="27" t="s">
         <v>133</v>
       </c>
-      <c r="B26" s="43" t="s">
+      <c r="B26" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="55" t="s">
+      <c r="C26" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="E26" s="47"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="47"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="47"/>
-      <c r="K26" s="47"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
-      <c r="N26" s="47"/>
-      <c r="O26" s="56" t="s">
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="36"/>
+      <c r="J26" s="36"/>
+      <c r="K26" s="36"/>
+      <c r="L26" s="36"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="45" t="s">
         <v>135</v>
       </c>
-      <c r="P26" s="57"/>
-      <c r="Q26" s="57"/>
-      <c r="R26" s="57"/>
-      <c r="S26" s="47"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="46"/>
+      <c r="R26" s="46"/>
+      <c r="S26" s="36"/>
     </row>
     <row r="27" spans="1:19" ht="15" customHeight="1">
-      <c r="A27" s="38" t="s">
+      <c r="A27" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="C27" s="67" t="s">
+      <c r="C27" s="56" t="s">
         <v>140</v>
       </c>
-      <c r="D27" s="38" t="s">
+      <c r="D27" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="68" t="s">
+      <c r="E27" s="36"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="57" t="s">
         <v>142</v>
       </c>
-      <c r="P27" s="69"/>
-      <c r="Q27" s="69"/>
-      <c r="R27" s="47"/>
-      <c r="S27" s="47"/>
+      <c r="P27" s="58"/>
+      <c r="Q27" s="58"/>
+      <c r="R27" s="36"/>
+      <c r="S27" s="36"/>
     </row>
     <row r="28" spans="1:19" ht="15" customHeight="1">
-      <c r="A28" s="38" t="s">
+      <c r="A28" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="B28" s="43" t="s">
+      <c r="B28" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="C28" s="67" t="s">
+      <c r="C28" s="56" t="s">
         <v>140</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="D28" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="47"/>
-      <c r="F28" s="47"/>
-      <c r="G28" s="47"/>
-      <c r="H28" s="47"/>
-      <c r="I28" s="47"/>
-      <c r="J28" s="47"/>
-      <c r="K28" s="47"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
-      <c r="N28" s="47"/>
-      <c r="O28" s="47"/>
-      <c r="P28" s="68" t="s">
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="36"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="36"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="36"/>
+      <c r="P28" s="57" t="s">
         <v>73</v>
       </c>
-      <c r="Q28" s="69"/>
-      <c r="R28" s="69"/>
-      <c r="S28" s="47"/>
+      <c r="Q28" s="58"/>
+      <c r="R28" s="58"/>
+      <c r="S28" s="36"/>
     </row>
     <row r="29" spans="1:19" ht="15" customHeight="1">
-      <c r="A29" s="38" t="s">
+      <c r="A29" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="B29" s="43" t="s">
+      <c r="B29" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="C29" s="67" t="s">
+      <c r="C29" s="56" t="s">
         <v>140</v>
       </c>
-      <c r="D29" s="38" t="s">
+      <c r="D29" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="E29" s="47"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="47"/>
-      <c r="H29" s="47"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="47"/>
-      <c r="K29" s="47"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
-      <c r="N29" s="47"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="47"/>
-      <c r="Q29" s="68" t="s">
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="36"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="36"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="36"/>
+      <c r="P29" s="36"/>
+      <c r="Q29" s="57" t="s">
         <v>152</v>
       </c>
-      <c r="R29" s="69"/>
-      <c r="S29" s="47"/>
+      <c r="R29" s="58"/>
+      <c r="S29" s="36"/>
     </row>
     <row r="30" spans="1:19" ht="15" customHeight="1">
-      <c r="A30" s="38" t="s">
+      <c r="A30" s="27" t="s">
         <v>156</v>
       </c>
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="C30" s="70" t="s">
+      <c r="C30" s="59" t="s">
         <v>157</v>
       </c>
-      <c r="D30" s="52" t="s">
+      <c r="D30" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E30" s="47"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="47"/>
-      <c r="H30" s="47"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="47"/>
-      <c r="K30" s="47"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
-      <c r="N30" s="47"/>
-      <c r="O30" s="47"/>
-      <c r="P30" s="47"/>
-      <c r="Q30" s="47"/>
-      <c r="R30" s="71" t="s">
+      <c r="E30" s="36"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="36"/>
+      <c r="J30" s="36"/>
+      <c r="K30" s="36"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="36"/>
+      <c r="P30" s="36"/>
+      <c r="Q30" s="36"/>
+      <c r="R30" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="S30" s="72"/>
+      <c r="S30" s="61"/>
     </row>
     <row r="31" spans="1:19" ht="15" customHeight="1">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="32" t="s">
         <v>163</v>
       </c>
-      <c r="C31" s="70" t="s">
+      <c r="C31" s="59" t="s">
         <v>157</v>
       </c>
-      <c r="D31" s="52" t="s">
+      <c r="D31" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="47"/>
-      <c r="K31" s="47"/>
-      <c r="L31" s="47"/>
-      <c r="M31" s="47"/>
-      <c r="N31" s="47"/>
-      <c r="O31" s="47"/>
-      <c r="P31" s="47"/>
-      <c r="Q31" s="47"/>
-      <c r="R31" s="47"/>
-      <c r="S31" s="71" t="s">
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="36"/>
+      <c r="I31" s="36"/>
+      <c r="J31" s="36"/>
+      <c r="K31" s="36"/>
+      <c r="L31" s="36"/>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="36"/>
+      <c r="Q31" s="36"/>
+      <c r="R31" s="36"/>
+      <c r="S31" s="60" t="s">
         <v>60</v>
       </c>
     </row>
@@ -7857,122 +7840,122 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="25.5" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="67" t="s">
         <v>197</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="62" t="s">
         <v>198</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="62" t="s">
         <v>199</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="62" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="73" t="s">
+      <c r="D2" s="62" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="26.25" customHeight="1">
-      <c r="A3" s="74" t="s">
+      <c r="A3" s="63" t="s">
         <v>202</v>
       </c>
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="64" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="76">
+      <c r="C3" s="65">
         <v>11</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="28" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="74" t="s">
+      <c r="A4" s="63" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="64" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="76">
+      <c r="C4" s="65">
         <v>9</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="28" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
-      <c r="A5" s="74" t="s">
+      <c r="A5" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="76">
+      <c r="C5" s="65">
         <v>8</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="28" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
-      <c r="A6" s="74" t="s">
+      <c r="A6" s="63" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="66" t="s">
         <v>209</v>
       </c>
-      <c r="C6" s="76">
+      <c r="C6" s="65">
         <v>9</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="28" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
-      <c r="A7" s="74" t="s">
+      <c r="A7" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="64" t="s">
         <v>211</v>
       </c>
-      <c r="C7" s="76">
+      <c r="C7" s="65">
         <v>11</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="28" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
-      <c r="A8" s="74" t="s">
+      <c r="A8" s="63" t="s">
         <v>66</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="64" t="s">
         <v>213</v>
       </c>
-      <c r="C8" s="76">
+      <c r="C8" s="65">
         <v>10</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="28" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
-      <c r="A9" s="74" t="s">
+      <c r="A9" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="64" t="s">
         <v>223</v>
       </c>
-      <c r="C9" s="76">
+      <c r="C9" s="65">
         <v>11</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="28" t="s">
         <v>215</v>
       </c>
     </row>
@@ -7995,108 +7978,108 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="77" t="s">
         <v>216</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A2" s="75"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
     </row>
     <row r="3" spans="1:8" ht="24" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="74" t="s">
         <v>217</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="B3" s="74"/>
+      <c r="C3" s="74"/>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="74"/>
+      <c r="G3" s="74"/>
+      <c r="H3" s="74"/>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="74" t="s">
         <v>218</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="74" t="s">
         <v>219</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
     </row>
     <row r="6" spans="1:8" ht="24" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="74" t="s">
         <v>220</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
     </row>
     <row r="7" spans="1:8" ht="24" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="74" t="s">
         <v>221</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
     </row>
     <row r="8" spans="1:8" ht="24" customHeight="1">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="A8" s="75"/>
+      <c r="B8" s="75"/>
+      <c r="C8" s="75"/>
+      <c r="D8" s="75"/>
+      <c r="E8" s="75"/>
+      <c r="F8" s="75"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="75"/>
     </row>
     <row r="9" spans="1:8" ht="24" customHeight="1">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="76" t="s">
         <v>222</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/工作分配.xlsx
+++ b/工作分配.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-6768" yWindow="12852" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工作分配總表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="甘特圖" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人力配置" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明與原則" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="工作分配總表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="甘特圖" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="人力配置" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="說明與原則" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -257,6 +257,7 @@
       <family val="2"/>
       <sz val="10"/>
     </font>
+    <font/>
   </fonts>
   <fills count="18">
     <fill>
@@ -362,7 +363,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -385,11 +386,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -600,6 +602,7 @@
     <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -859,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="2"/>
@@ -994,7 +997,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J4" s="7">
         <f>I4-H4+1</f>
@@ -1058,7 +1061,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5" s="7">
         <f>I5-H5+1</f>
@@ -1124,7 +1127,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" s="7">
         <f>I6-H6+1</f>
@@ -1185,7 +1188,7 @@
         </is>
       </c>
       <c r="H7" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>5</v>
@@ -1409,7 +1412,7 @@
     <row r="11" ht="87.75" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>T07</t>
+          <t>T08</t>
         </is>
       </c>
       <c r="B11" s="11" t="inlineStr">
@@ -1417,114 +1420,50 @@
           <t>第一週</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>向量化/去重</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Embedding 技術實驗（凍結樣本，全員玩）</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>全員</t>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>前端/UX</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>使用者旅程 + 線框圖（4 畫面）</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>高</t>
+        <v>1</v>
+      </c>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H11" s="7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J11" s="7">
-        <f>I11-H11+1</f>
-        <v/>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>各自實驗心得 + 凍結樣本</t>
-        </is>
-      </c>
-      <c r="M11" s="10" t="inlineStr">
-        <is>
-          <t>• 環境：本機 venv + pip install FlagEmbedding；**不需資料庫**（用樣本檔）
-• 前置：Arku 先給約 500 篇清洗好文章，匯成 data/samples/articles_frozen.jsonl（全員同一份）
-• 在哪：各自在 experiments_everyone/ 開 notebook 玩，拋棄式
-• 界線：實驗向量留本機，別進正式 Postgres
-• 交什麼：一頁心得（模型/維度/前處理/閾值觀察）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="73.5" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>T08</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>第一週</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>前端/UX</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>使用者旅程 + 線框圖（4 畫面）</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>Jenny</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="7">
         <f>I12-H12+1</f>
         <v/>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>3 條旅程 + wireframe</t>
         </is>
       </c>
-      <c r="M12" s="10" t="inlineStr">
+      <c r="M11" s="10" t="inlineStr">
         <is>
           <t>• 環境：無（設計），用 Figma 或紙筆
 • 前置：讀 01_PRD 線框圖與三條旅程
@@ -1533,61 +1472,61 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="73.5" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12" ht="73.5" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>T09</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>第一週</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>評分/籌碼</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>FinMind 資料源研究 + 認證測試</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Bright</t>
         </is>
       </c>
-      <c r="F13" s="7" t="n">
+      <c r="F12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G12" s="19" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H13" s="7" t="n">
+      <c r="H12" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="I12" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J12" s="7">
         <f>I13-H13+1</f>
         <v/>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="L12" s="9" t="inlineStr">
         <is>
           <t>取數可行性報告</t>
         </is>
       </c>
-      <c r="M13" s="10" t="inlineStr">
+      <c r="M12" s="10" t="inlineStr">
         <is>
           <t>• 你之前用過 FinMind，快速確認即可（2 天）
 • token 放 .env 的 FINMIND_TOKEN
@@ -1596,61 +1535,61 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="87.75" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="13" ht="73.5" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>T10</t>
         </is>
       </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>第二週</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>資料來源/爬蟲</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>爬蟲正式化 + ticker 標註 + 寫入 articles 表</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>Arku</t>
         </is>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="F13" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H14" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="J14" s="7">
+      <c r="H13" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="7">
         <f>I14-H14+1</f>
         <v/>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>T06</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>articles 表持續進資料</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M13" s="10" t="inlineStr">
         <is>
           <t>• ★ 環境：務必先確認 Nash 的 db 起來（compose up -d db）+ articles 表建好(T03)
 • 本機 .env 設 DATABASE_URL，全員連同一個 db
@@ -1660,61 +1599,61 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="87.75" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="14" ht="87.75" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>T11</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>第二週</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>向量化/去重</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Embedding 心得整合 + BGE-M3 定案</t>
         </is>
       </c>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Timyo</t>
         </is>
       </c>
-      <c r="F15" s="7" t="n">
+      <c r="F14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H15" s="7" t="n">
+      <c r="H14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="I15" s="7" t="n">
+      <c r="I14" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="J15" s="7">
+      <c r="J14" s="7">
         <f>I15-H15+1</f>
         <v/>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>T07</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>定案參數(模型/維度/前處理/閾值)</t>
         </is>
       </c>
-      <c r="M15" s="10" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>• ★ 環境：需 db(T01)+events 表(T03)；模型檔放 data/models/（別進 git）
 • 前置：彙整 T07 全員心得
@@ -1724,61 +1663,61 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="73.5" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15" ht="87.75" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>T12</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>第二週</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>向量化/去重</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>去重聚類實作（Cosine&gt;0.65 + 連通分量）</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>Timyo</t>
         </is>
       </c>
-      <c r="F16" s="7" t="n">
+      <c r="F15" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H16" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" s="7">
+      <c r="H15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="7">
         <f>I16-H16+1</f>
         <v/>
       </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>T11</t>
-        </is>
-      </c>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>樣本就緒</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>多篇收斂成事件物件</t>
         </is>
       </c>
-      <c r="M16" s="10" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>• ★ 環境：需 db + events 表(T03)，且已有向量(status=vectorized)
 • 做什麼：Cosine&gt;0.65 + 連通分量 → 合併成事件物件
@@ -1787,61 +1726,61 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="87.75" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="16" ht="73.5" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>T13</t>
         </is>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>第一週</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>LLM 摘要/分類</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Prompt 設計（摘要 + 9類分類 + 方向，同一次）</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>MMJSUN</t>
         </is>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H17" s="7" t="n">
+      <c r="H16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J17" s="7">
+      <c r="I16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" s="7">
         <f>I17-H17+1</f>
         <v/>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L17" s="9" t="inlineStr">
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>可用 prompt 範本</t>
         </is>
       </c>
-      <c r="M17" s="10" t="inlineStr">
+      <c r="M16" s="10" t="inlineStr">
         <is>
           <t>• ★ 環境：需 db + events 表(T03) + .env 的 LLM_API_KEY
 • 前置：讀 07_Prompt範本
@@ -1851,61 +1790,61 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="87.75" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="17" ht="87.75" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>T14</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>第二週</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>LLM 摘要/分類</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>LLM 選型 + Structured Output 整合</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>MMJSUN</t>
         </is>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F17" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G17" s="19" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H18" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" s="7">
+      <c r="H17" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="7">
         <f>I18-H18+1</f>
         <v/>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>T13</t>
         </is>
       </c>
-      <c r="L18" s="9" t="inlineStr">
+      <c r="L17" s="9" t="inlineStr">
         <is>
           <t>穩定 JSON 輸出模組</t>
         </is>
       </c>
-      <c r="M18" s="10" t="inlineStr">
+      <c r="M17" s="10" t="inlineStr">
         <is>
           <t>• 環境：同 T13（需 LLM_API_KEY）
 • 前置：T13 prompt 就緒
@@ -1915,63 +1854,64 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="87.75" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18" ht="87.75" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>T15</t>
         </is>
       </c>
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>第二週</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>評分/籌碼</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>重要性五維評分（可拆解）</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Bright</t>
         </is>
       </c>
-      <c r="F19" s="7" t="n">
+      <c r="F18" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H19" s="7" t="n">
+      <c r="H18" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I18" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="I19" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="J19" s="7">
+      <c r="J18" s="7">
         <f>I19-H19+1</f>
         <v/>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>T03</t>
-        </is>
-      </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>樣本就緒</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>★1-5 + 理由拆解</t>
         </is>
       </c>
-      <c r="M19" s="10" t="inlineStr">
-        <is>
-          <t>• ★ 環境：需 db + events 表(T03)
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>【可先起手】五維為純函數，可先寫框架+用假事件(冻结樣本)測；真打分需事件資料(去重T12/LLM T13-14 產出)，別空等。 
+• ★ 環境：需 db + events 表(T03)
 • 檔案：backend/app/pipeline/scoring_Bright/importance.py
 • 做什麼：五維加權（來源廣度/權威/影響/類型/新穎）→ ★1-5
 • 鐵律：每個分數要能拆解理由，不能只給星等
@@ -1979,61 +1919,61 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="87.75" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="19" ht="87.75" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>T16</t>
         </is>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>第二週</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>評分/籌碼</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>FinMind 每日批次 + ChipData 衍生欄位</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Bright</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n">
+      <c r="F19" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G19" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H20" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" s="7">
+      <c r="H19" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" s="7">
         <f>I20-H20+1</f>
         <v/>
       </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>T09</t>
-        </is>
-      </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>ChipData(連續天數/占均量/σ/報酬)</t>
         </is>
       </c>
-      <c r="M20" s="10" t="inlineStr">
+      <c r="M19" s="10" t="inlineStr">
         <is>
           <t>• ★ 環境：需 db + chip_data 表(T03) + .env 的 FINMIND_TOKEN
 • 檔案：backend/app/finmind_Bright/{client,daily_batch}.py
@@ -2043,63 +1983,64 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="87.75" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="20" ht="87.75" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>T17</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>第二週</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>評分/籌碼</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>市場驗證分數（三訊號 + 一致性閘門 + 狀態機）</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Bright·Nash·MMJSUN</t>
         </is>
       </c>
-      <c r="F21" s="7" t="n">
+      <c r="F20" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H21" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="J21" s="7">
+      <c r="H20" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" s="7">
         <f>I21-H21+1</f>
         <v/>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>T16</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>樣本就緒</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>0-100 分 + 可拆解 breakdown</t>
         </is>
       </c>
-      <c r="M21" s="10" t="inlineStr">
-        <is>
-          <t>• ★ 環境：需 db + chip_data/events 表(T03)，且 T16 ChipData 已入庫
+      <c r="M20" s="10" t="inlineStr">
+        <is>
+          <t>【提前｜FinMind已就緒】評分邏輯只吃 chip_data，可用本地 chip_data/CSV 先開發驗證，不必等 T16 落庫與 events 表；分數寫回 events 那步再接。 
+• ★ 環境：需 db + chip_data/events 表(T03)，且 T16 ChipData 已入庫
 • 檔案：backend/app/pipeline/scoring_Bright/market_validation.py
 • 做什麼：三訊號一致性×強度 + 一致性閘門 + 狀態機(D0→D+5) → 0-100
 • 定案前：分數方向與閾值先與 Haoche 對一次再實作（這塊最主觀，先對齊省得重做）
@@ -2107,61 +2048,61 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="73.5" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="21" ht="87.75" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>T18</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>第二週</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C21" s="18" t="inlineStr">
         <is>
           <t>前端/UX</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>前端框架初始化 + 首頁（Mock 資料）</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Jenny</t>
         </is>
       </c>
-      <c r="F22" s="7" t="n">
+      <c r="F21" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H22" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="J22" s="7">
+      <c r="H21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J21" s="7">
         <f>I22-H22+1</f>
         <v/>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>T04</t>
         </is>
       </c>
-      <c r="L22" s="9" t="inlineStr">
+      <c r="L21" s="9" t="inlineStr">
         <is>
           <t>今日 5 大事件首頁</t>
         </is>
       </c>
-      <c r="M22" s="10" t="inlineStr">
+      <c r="M21" s="10" t="inlineStr">
         <is>
           <t>• ★ 環境：需 T04 的 Mock API 跑起來（uvicorn）；前端 npm install
 • 做什麼：前端框架初始化，做「今日 5 大事件」首頁先串 Mock
@@ -2170,61 +2111,61 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="87.75" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="22" ht="73.5" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>T19</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>第二週</t>
         </is>
       </c>
-      <c r="C23" s="12" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>地基/架構</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>FastAPI 端點實作（讀 DB）</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>Nash·Jenny·Haoche</t>
         </is>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="F22" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H23" s="7" t="n">
+      <c r="H22" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I23" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="J23" s="7">
+      <c r="J22" s="7">
         <f>I23-H23+1</f>
         <v/>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>T03,T04</t>
-        </is>
-      </c>
-      <c r="L23" s="9" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>T03</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
         <is>
           <t>只讀 API 回真資料</t>
         </is>
       </c>
-      <c r="M23" s="14" t="inlineStr">
+      <c r="M22" s="14" t="inlineStr">
         <is>
           <t>• ★ 環境：需 db + 三張表(T03) + 契約(T04)
 • 檔案：backend/app/api/{events,tickers}.py
@@ -2234,61 +2175,61 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="73.5" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="23" ht="87.75" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>T20</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>第三週</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>整合</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>端到端串接（英雄場景：台積電法說）</t>
         </is>
       </c>
-      <c r="E24" s="17" t="inlineStr">
+      <c r="E23" s="17" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="F24" s="7" t="n">
+      <c r="F23" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H24" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="J24" s="7">
+      <c r="H23" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J23" s="7">
         <f>I24-H24+1</f>
         <v/>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>T12,T17,T19</t>
         </is>
       </c>
-      <c r="L24" s="9" t="inlineStr">
+      <c r="L23" s="9" t="inlineStr">
         <is>
           <t>全程跑通一個事件</t>
         </is>
       </c>
-      <c r="M24" s="10" t="inlineStr">
+      <c r="M23" s="10" t="inlineStr">
         <is>
           <t>• ★ 環境：db + 全部表 + 各模組就緒(T12/T17/T19)；全員本機連同一個 db
 • 目標：台積電法說一個事件，從爬蟲跑到市場驗證分數、前端看得到
@@ -2297,61 +2238,61 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="87.75" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="24" ht="73.5" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>T21</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>第三週</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>整合</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>APScheduler 排程整合（管線每輪 + 每日批次）</t>
         </is>
       </c>
-      <c r="E25" s="13" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Arku·Bright</t>
         </is>
       </c>
-      <c r="F25" s="7" t="n">
+      <c r="F24" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H25" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="J25" s="7">
+      <c r="H24" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J24" s="7">
         <f>I25-H25+1</f>
         <v/>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>T19</t>
         </is>
       </c>
-      <c r="L25" s="9" t="inlineStr">
+      <c r="L24" s="9" t="inlineStr">
         <is>
           <t>自動排程跑管線</t>
         </is>
       </c>
-      <c r="M25" s="10" t="inlineStr">
+      <c r="M24" s="10" t="inlineStr">
         <is>
           <t>• ★ 環境：管線可手動跑通、db 就緒；worker 服務的 Dockerfile 由你(Arku)補
 • 檔案：backend/app/core/scheduler.py（APScheduler）
@@ -2361,61 +2302,61 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="25" ht="87.75" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>T22</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>第三週</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>前端/UX</t>
         </is>
       </c>
-      <c r="D26" s="9" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>事件詳情頁 + 籌碼拆解 + 搜尋/時間線</t>
         </is>
       </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Jenny·MMJSUN</t>
         </is>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F25" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="8" t="inlineStr">
+      <c r="G25" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H26" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="I26" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="J26" s="7">
+      <c r="H25" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J25" s="7">
         <f>I26-H26+1</f>
         <v/>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>T18,T19</t>
         </is>
       </c>
-      <c r="L26" s="9" t="inlineStr">
+      <c r="L25" s="9" t="inlineStr">
         <is>
           <t>完整 4 畫面串真 API</t>
         </is>
       </c>
-      <c r="M26" s="10" t="inlineStr">
+      <c r="M25" s="10" t="inlineStr">
         <is>
           <t>• ★ 環境：需 T18 首頁 + T19 真 API 已可回資料
 • 做什麼：詳情頁（摘要+市場驗證分數+籌碼拆解）、搜尋、時間線
@@ -2423,61 +2364,61 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="73.5" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>T23</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>第三週</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>驗證</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>去重 F1 / 分類準確率 驗證</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Timyo·MMJSUN</t>
         </is>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F26" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="19" t="inlineStr">
+      <c r="G26" s="19" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H27" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="I27" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="J27" s="7">
+      <c r="H26" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J26" s="7">
         <f>I27-H27+1</f>
         <v/>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>T12,T14</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>F1 / micro-F1 報告</t>
         </is>
       </c>
-      <c r="M27" s="10" t="inlineStr">
+      <c r="M26" s="10" t="inlineStr">
         <is>
           <t>• 環境：需 T12 去重、T14 分類產出可跑
 • 前置：人工標 golden set
@@ -2486,61 +2427,61 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="73.5" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="27" ht="73.5" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>T24</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>第三週</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>驗證</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>評分行為合理性驗證（跨天平滑/分歧閘門）</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Bright</t>
         </is>
       </c>
-      <c r="F28" s="7" t="n">
+      <c r="F27" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G27" s="19" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H28" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="I28" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="J28" s="7">
+      <c r="H27" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J27" s="7">
         <f>I28-H28+1</f>
         <v/>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>T17</t>
         </is>
       </c>
-      <c r="L28" s="9" t="inlineStr">
+      <c r="L27" s="9" t="inlineStr">
         <is>
           <t>驗證報告</t>
         </is>
       </c>
-      <c r="M28" s="10" t="inlineStr">
+      <c r="M27" s="10" t="inlineStr">
         <is>
           <t>• 環境：需 T17 分數已能算
 • 檢查：同事件跨天分數是否平滑、分歧閘門能否抓到已知背離
@@ -2549,61 +2490,61 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="28" ht="73.5" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>T25</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>第三週</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>驗證</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>全套 Docker Compose up 整合測試</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Nash·Arku·Haoche</t>
         </is>
       </c>
-      <c r="F29" s="7" t="n">
+      <c r="F28" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H29" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="I29" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="J29" s="7">
+      <c r="H28" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J28" s="7">
         <f>I29-H29+1</f>
         <v/>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>T20,T21</t>
         </is>
       </c>
-      <c r="L29" s="9" t="inlineStr">
+      <c r="L28" s="9" t="inlineStr">
         <is>
           <t>一行 up 全套跑起來</t>
         </is>
       </c>
-      <c r="M29" s="10" t="inlineStr">
+      <c r="M28" s="10" t="inlineStr">
         <is>
           <t>• ★ 環境：T20/T21 完成；把 api、worker 的 Dockerfile 補上
 • 目標：一行 docker compose up 起 db+api+worker 全套
@@ -2611,61 +2552,61 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>T26</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>第三週</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C29" s="25" t="inlineStr">
         <is>
           <t>收尾</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Demo 準備 + 文件整理</t>
         </is>
       </c>
-      <c r="E30" s="17" t="inlineStr">
+      <c r="E29" s="17" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F29" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H30" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="I30" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="J30" s="7">
+      <c r="H29" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J29" s="7">
         <f>I30-H30+1</f>
         <v/>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>T22,T25</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>Demo 流程 + 文件</t>
         </is>
       </c>
-      <c r="M30" s="10" t="inlineStr">
+      <c r="M29" s="10" t="inlineStr">
         <is>
           <t>• 環境：T22/T25 完成
 • 準備：Demo 腳本、跑一次英雄場景、整理 README/文件
@@ -2673,67 +2614,68 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="45.75" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>T27</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>第三週</t>
         </is>
       </c>
-      <c r="C31" s="25" t="inlineStr">
+      <c r="C30" s="25" t="inlineStr">
         <is>
           <t>收尾</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>緩衝 / Bug 修復</t>
         </is>
       </c>
-      <c r="E31" s="17" t="inlineStr">
+      <c r="E30" s="17" t="inlineStr">
         <is>
           <t>全員</t>
         </is>
       </c>
-      <c r="F31" s="7" t="n">
+      <c r="F30" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G31" s="19" t="inlineStr">
+      <c r="G30" s="19" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H31" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="J31" s="7">
+      <c r="H30" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J30" s="7">
         <f>I31-H31+1</f>
         <v/>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M31" s="10" t="inlineStr">
+      <c r="M30" s="10" t="inlineStr">
         <is>
           <t>• 用途：吸收前面延遲、修 demo 前發現的 bug
 • 界線：只修 bug，不加新功能</t>
         </is>
       </c>
     </row>
+    <row r="31" ht="45.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
@@ -2750,7 +2692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3031,12 +2973,12 @@
         </is>
       </c>
       <c r="E7" s="36" t="n"/>
-      <c r="F7" s="34" t="inlineStr">
+      <c r="F7" s="78" t="n"/>
+      <c r="G7" s="34" t="inlineStr">
         <is>
           <t>Nash·Bright·Haoche</t>
         </is>
       </c>
-      <c r="G7" s="35" t="n"/>
       <c r="H7" s="35" t="n"/>
       <c r="I7" s="35" t="n"/>
       <c r="J7" s="36" t="n"/>
@@ -3176,34 +3118,34 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="27" t="inlineStr">
         <is>
-          <t>T07</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="inlineStr">
-        <is>
-          <t>Embedding 技術實驗（凍結樣本，全員玩）</t>
-        </is>
-      </c>
-      <c r="C11" s="40" t="inlineStr">
-        <is>
-          <t>向量化/去重</t>
-        </is>
-      </c>
-      <c r="D11" s="41" t="inlineStr">
-        <is>
-          <t>全員</t>
-        </is>
-      </c>
-      <c r="E11" s="36" t="n"/>
-      <c r="F11" s="36" t="n"/>
-      <c r="G11" s="36" t="n"/>
-      <c r="H11" s="42" t="inlineStr">
-        <is>
-          <t>全員</t>
-        </is>
-      </c>
-      <c r="I11" s="43" t="n"/>
-      <c r="J11" s="43" t="n"/>
+          <t>T08</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>使用者旅程 + 線框圖（4 畫面）</t>
+        </is>
+      </c>
+      <c r="C11" s="44" t="inlineStr">
+        <is>
+          <t>前端/UX</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="E11" s="45" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
+      <c r="F11" s="46" t="n"/>
+      <c r="G11" s="46" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
+      <c r="J11" s="36" t="n"/>
       <c r="K11" s="36" t="n"/>
       <c r="L11" s="36" t="n"/>
       <c r="M11" s="36" t="n"/>
@@ -3217,31 +3159,31 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="27" t="inlineStr">
         <is>
-          <t>T08</t>
-        </is>
-      </c>
-      <c r="B12" s="32" t="inlineStr">
-        <is>
-          <t>使用者旅程 + 線框圖（4 畫面）</t>
-        </is>
-      </c>
-      <c r="C12" s="44" t="inlineStr">
-        <is>
-          <t>前端/UX</t>
+          <t>T09</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>FinMind 資料源研究 + 認證測試</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="inlineStr">
+        <is>
+          <t>評分/籌碼</t>
         </is>
       </c>
       <c r="D12" s="27" t="inlineStr">
         <is>
-          <t>Jenny</t>
-        </is>
-      </c>
-      <c r="E12" s="45" t="inlineStr">
-        <is>
-          <t>Jenny</t>
-        </is>
-      </c>
-      <c r="F12" s="46" t="n"/>
-      <c r="G12" s="46" t="n"/>
+          <t>Bright</t>
+        </is>
+      </c>
+      <c r="E12" s="48" t="inlineStr">
+        <is>
+          <t>Bright</t>
+        </is>
+      </c>
+      <c r="F12" s="49" t="n"/>
+      <c r="G12" s="50" t="n"/>
       <c r="H12" s="36" t="n"/>
       <c r="I12" s="36" t="n"/>
       <c r="J12" s="36" t="n"/>
@@ -3258,37 +3200,37 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>T09</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="inlineStr">
-        <is>
-          <t>FinMind 資料源研究 + 認證測試</t>
-        </is>
-      </c>
-      <c r="C13" s="47" t="inlineStr">
-        <is>
-          <t>評分/籌碼</t>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>爬蟲正式化 + ticker 標註 + 寫入 articles 表</t>
+        </is>
+      </c>
+      <c r="C13" s="37" t="inlineStr">
+        <is>
+          <t>資料來源/爬蟲</t>
         </is>
       </c>
       <c r="D13" s="27" t="inlineStr">
         <is>
-          <t>Bright</t>
-        </is>
-      </c>
-      <c r="E13" s="48" t="inlineStr">
-        <is>
-          <t>Bright</t>
-        </is>
-      </c>
-      <c r="F13" s="49" t="n"/>
-      <c r="G13" s="50" t="n"/>
-      <c r="H13" s="36" t="n"/>
+          <t>Arku</t>
+        </is>
+      </c>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="38" t="inlineStr">
+        <is>
+          <t>Arku</t>
+        </is>
+      </c>
       <c r="I13" s="36" t="n"/>
-      <c r="J13" s="36" t="n"/>
-      <c r="K13" s="36" t="n"/>
-      <c r="L13" s="36" t="n"/>
-      <c r="M13" s="36" t="n"/>
+      <c r="J13" s="78" t="n"/>
+      <c r="K13" s="39" t="n"/>
+      <c r="L13" s="39" t="n"/>
+      <c r="M13" s="39" t="n"/>
       <c r="N13" s="36" t="n"/>
       <c r="O13" s="36" t="n"/>
       <c r="P13" s="36" t="n"/>
@@ -3299,22 +3241,22 @@
     <row r="14" ht="26.25" customHeight="1">
       <c r="A14" s="27" t="inlineStr">
         <is>
-          <t>T10</t>
-        </is>
-      </c>
-      <c r="B14" s="32" t="inlineStr">
-        <is>
-          <t>爬蟲正式化 + ticker 標註 + 寫入 articles 表</t>
-        </is>
-      </c>
-      <c r="C14" s="37" t="inlineStr">
-        <is>
-          <t>資料來源/爬蟲</t>
+          <t>T11</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Embedding 心得整合 + BGE-M3 定案</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>向量化/去重</t>
         </is>
       </c>
       <c r="D14" s="27" t="inlineStr">
         <is>
-          <t>Arku</t>
+          <t>Timyo·MMJSUN</t>
         </is>
       </c>
       <c r="E14" s="36" t="n"/>
@@ -3322,14 +3264,14 @@
       <c r="G14" s="36" t="n"/>
       <c r="H14" s="36" t="n"/>
       <c r="I14" s="36" t="n"/>
-      <c r="J14" s="38" t="inlineStr">
-        <is>
-          <t>Arku</t>
-        </is>
-      </c>
-      <c r="K14" s="39" t="n"/>
-      <c r="L14" s="39" t="n"/>
-      <c r="M14" s="39" t="n"/>
+      <c r="J14" s="51" t="inlineStr">
+        <is>
+          <t>Timyo</t>
+        </is>
+      </c>
+      <c r="K14" s="43" t="n"/>
+      <c r="L14" s="36" t="n"/>
+      <c r="M14" s="36" t="n"/>
       <c r="N14" s="36" t="n"/>
       <c r="O14" s="36" t="n"/>
       <c r="P14" s="36" t="n"/>
@@ -3340,12 +3282,12 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>T11</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="inlineStr">
-        <is>
-          <t>Embedding 心得整合 + BGE-M3 定案</t>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>去重聚類實作（Cosine&gt;0.65 + 連通分量）</t>
         </is>
       </c>
       <c r="C15" s="40" t="inlineStr">
@@ -3355,23 +3297,23 @@
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>Timyo·MMJSUN</t>
+          <t>Timyo</t>
         </is>
       </c>
       <c r="E15" s="36" t="n"/>
       <c r="F15" s="36" t="n"/>
-      <c r="G15" s="36" t="n"/>
+      <c r="G15" s="51" t="inlineStr">
+        <is>
+          <t>Timyo</t>
+        </is>
+      </c>
       <c r="H15" s="36" t="n"/>
       <c r="I15" s="36" t="n"/>
-      <c r="J15" s="51" t="inlineStr">
-        <is>
-          <t>Timyo</t>
-        </is>
-      </c>
-      <c r="K15" s="43" t="n"/>
-      <c r="L15" s="36" t="n"/>
-      <c r="M15" s="36" t="n"/>
-      <c r="N15" s="36" t="n"/>
+      <c r="J15" s="36" t="n"/>
+      <c r="K15" s="78" t="n"/>
+      <c r="L15" s="43" t="n"/>
+      <c r="M15" s="43" t="n"/>
+      <c r="N15" s="43" t="n"/>
       <c r="O15" s="36" t="n"/>
       <c r="P15" s="36" t="n"/>
       <c r="Q15" s="36" t="n"/>
@@ -3381,38 +3323,38 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="B16" s="32" t="inlineStr">
-        <is>
-          <t>去重聚類實作（Cosine&gt;0.65 + 連通分量）</t>
-        </is>
-      </c>
-      <c r="C16" s="40" t="inlineStr">
-        <is>
-          <t>向量化/去重</t>
+          <t>T13</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Prompt 設計（摘要 + 9類分類 + 方向，同一次）</t>
+        </is>
+      </c>
+      <c r="C16" s="52" t="inlineStr">
+        <is>
+          <t>LLM 摘要/分類</t>
         </is>
       </c>
       <c r="D16" s="27" t="inlineStr">
         <is>
-          <t>Timyo</t>
-        </is>
-      </c>
-      <c r="E16" s="36" t="n"/>
-      <c r="F16" s="36" t="n"/>
-      <c r="G16" s="36" t="n"/>
-      <c r="H16" s="36" t="n"/>
-      <c r="I16" s="36" t="n"/>
+          <t>MMJSUN</t>
+        </is>
+      </c>
+      <c r="E16" s="53" t="inlineStr">
+        <is>
+          <t>MMJSUN</t>
+        </is>
+      </c>
+      <c r="F16" s="54" t="n"/>
+      <c r="G16" s="54" t="n"/>
+      <c r="H16" s="54" t="n"/>
+      <c r="I16" s="54" t="n"/>
       <c r="J16" s="36" t="n"/>
-      <c r="K16" s="51" t="inlineStr">
-        <is>
-          <t>Timyo</t>
-        </is>
-      </c>
-      <c r="L16" s="43" t="n"/>
-      <c r="M16" s="43" t="n"/>
-      <c r="N16" s="43" t="n"/>
+      <c r="K16" s="36" t="n"/>
+      <c r="L16" s="36" t="n"/>
+      <c r="M16" s="36" t="n"/>
+      <c r="N16" s="36" t="n"/>
       <c r="O16" s="36" t="n"/>
       <c r="P16" s="36" t="n"/>
       <c r="Q16" s="36" t="n"/>
@@ -3422,12 +3364,12 @@
     <row r="17" ht="26.25" customHeight="1">
       <c r="A17" s="27" t="inlineStr">
         <is>
-          <t>T13</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B17" s="28" t="inlineStr">
         <is>
-          <t>Prompt 設計（摘要 + 9類分類 + 方向，同一次）</t>
+          <t>LLM 選型 + Structured Output 整合</t>
         </is>
       </c>
       <c r="C17" s="52" t="inlineStr">
@@ -3440,20 +3382,20 @@
           <t>MMJSUN</t>
         </is>
       </c>
-      <c r="E17" s="53" t="inlineStr">
+      <c r="E17" s="36" t="n"/>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="53" t="inlineStr">
         <is>
           <t>MMJSUN</t>
         </is>
       </c>
-      <c r="F17" s="54" t="n"/>
-      <c r="G17" s="54" t="n"/>
-      <c r="H17" s="54" t="n"/>
-      <c r="I17" s="54" t="n"/>
+      <c r="I17" s="36" t="n"/>
       <c r="J17" s="36" t="n"/>
       <c r="K17" s="36" t="n"/>
-      <c r="L17" s="36" t="n"/>
-      <c r="M17" s="36" t="n"/>
-      <c r="N17" s="36" t="n"/>
+      <c r="L17" s="78" t="n"/>
+      <c r="M17" s="54" t="n"/>
+      <c r="N17" s="54" t="n"/>
       <c r="O17" s="36" t="n"/>
       <c r="P17" s="36" t="n"/>
       <c r="Q17" s="36" t="n"/>
@@ -3463,38 +3405,38 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="27" t="inlineStr">
         <is>
-          <t>T14</t>
-        </is>
-      </c>
-      <c r="B18" s="28" t="inlineStr">
-        <is>
-          <t>LLM 選型 + Structured Output 整合</t>
-        </is>
-      </c>
-      <c r="C18" s="52" t="inlineStr">
-        <is>
-          <t>LLM 摘要/分類</t>
+          <t>T15</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>重要性五維評分（可拆解）</t>
+        </is>
+      </c>
+      <c r="C18" s="47" t="inlineStr">
+        <is>
+          <t>評分/籌碼</t>
         </is>
       </c>
       <c r="D18" s="27" t="inlineStr">
         <is>
-          <t>MMJSUN</t>
+          <t>Bright·MMJSUN</t>
         </is>
       </c>
       <c r="E18" s="36" t="n"/>
       <c r="F18" s="36" t="n"/>
       <c r="G18" s="36" t="n"/>
-      <c r="H18" s="36" t="n"/>
+      <c r="H18" s="48" t="inlineStr">
+        <is>
+          <t>Bright</t>
+        </is>
+      </c>
       <c r="I18" s="36" t="n"/>
-      <c r="J18" s="36" t="n"/>
-      <c r="K18" s="36" t="n"/>
-      <c r="L18" s="53" t="inlineStr">
-        <is>
-          <t>MMJSUN</t>
-        </is>
-      </c>
-      <c r="M18" s="54" t="n"/>
-      <c r="N18" s="54" t="n"/>
+      <c r="J18" s="78" t="n"/>
+      <c r="K18" s="49" t="n"/>
+      <c r="L18" s="49" t="n"/>
+      <c r="M18" s="49" t="n"/>
+      <c r="N18" s="36" t="n"/>
       <c r="O18" s="36" t="n"/>
       <c r="P18" s="36" t="n"/>
       <c r="Q18" s="36" t="n"/>
@@ -3504,12 +3446,12 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="27" t="inlineStr">
         <is>
-          <t>T15</t>
-        </is>
-      </c>
-      <c r="B19" s="32" t="inlineStr">
-        <is>
-          <t>重要性五維評分（可拆解）</t>
+          <t>T16</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>FinMind 每日批次 + ChipData 衍生欄位</t>
         </is>
       </c>
       <c r="C19" s="47" t="inlineStr">
@@ -3519,22 +3461,22 @@
       </c>
       <c r="D19" s="27" t="inlineStr">
         <is>
-          <t>Bright·MMJSUN</t>
+          <t>Bright</t>
         </is>
       </c>
       <c r="E19" s="36" t="n"/>
-      <c r="F19" s="36" t="n"/>
-      <c r="G19" s="36" t="n"/>
-      <c r="H19" s="36" t="n"/>
-      <c r="I19" s="36" t="n"/>
-      <c r="J19" s="48" t="inlineStr">
+      <c r="F19" s="48" t="inlineStr">
         <is>
           <t>Bright</t>
         </is>
       </c>
-      <c r="K19" s="49" t="n"/>
-      <c r="L19" s="49" t="n"/>
-      <c r="M19" s="49" t="n"/>
+      <c r="G19" s="78" t="n"/>
+      <c r="H19" s="49" t="n"/>
+      <c r="I19" s="49" t="n"/>
+      <c r="J19" s="48" t="n"/>
+      <c r="K19" s="36" t="n"/>
+      <c r="L19" s="36" t="n"/>
+      <c r="M19" s="36" t="n"/>
       <c r="N19" s="36" t="n"/>
       <c r="O19" s="36" t="n"/>
       <c r="P19" s="36" t="n"/>
@@ -3545,12 +3487,12 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="27" t="inlineStr">
         <is>
-          <t>T16</t>
-        </is>
-      </c>
-      <c r="B20" s="28" t="inlineStr">
-        <is>
-          <t>FinMind 每日批次 + ChipData 衍生欄位</t>
+          <t>T17</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>市場驗證分數（三訊號 + 一致性閘門 + 狀態機）</t>
         </is>
       </c>
       <c r="C20" s="47" t="inlineStr">
@@ -3560,24 +3502,24 @@
       </c>
       <c r="D20" s="27" t="inlineStr">
         <is>
-          <t>Bright</t>
+          <t>Bright·Nash·MMJSUN</t>
         </is>
       </c>
       <c r="E20" s="36" t="n"/>
       <c r="F20" s="36" t="n"/>
-      <c r="G20" s="48" t="inlineStr">
-        <is>
-          <t>Bright</t>
-        </is>
-      </c>
-      <c r="H20" s="49" t="n"/>
-      <c r="I20" s="49" t="n"/>
-      <c r="J20" s="48" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="48" t="inlineStr">
+        <is>
+          <t>Bright·Nash·MMJSUN</t>
+        </is>
+      </c>
+      <c r="I20" s="36" t="n"/>
+      <c r="J20" s="36" t="n"/>
       <c r="K20" s="36" t="n"/>
-      <c r="L20" s="36" t="n"/>
-      <c r="M20" s="36" t="n"/>
-      <c r="N20" s="36" t="n"/>
-      <c r="O20" s="36" t="n"/>
+      <c r="L20" s="78" t="n"/>
+      <c r="M20" s="49" t="n"/>
+      <c r="N20" s="49" t="n"/>
+      <c r="O20" s="49" t="n"/>
       <c r="P20" s="36" t="n"/>
       <c r="Q20" s="36" t="n"/>
       <c r="R20" s="36" t="n"/>
@@ -3586,39 +3528,39 @@
     <row r="21" ht="26.25" customHeight="1">
       <c r="A21" s="27" t="inlineStr">
         <is>
-          <t>T17</t>
+          <t>T18</t>
         </is>
       </c>
       <c r="B21" s="32" t="inlineStr">
         <is>
-          <t>市場驗證分數（三訊號 + 一致性閘門 + 狀態機）</t>
-        </is>
-      </c>
-      <c r="C21" s="47" t="inlineStr">
-        <is>
-          <t>評分/籌碼</t>
+          <t>前端框架初始化 + 首頁（Mock 資料）</t>
+        </is>
+      </c>
+      <c r="C21" s="44" t="inlineStr">
+        <is>
+          <t>前端/UX</t>
         </is>
       </c>
       <c r="D21" s="27" t="inlineStr">
         <is>
-          <t>Bright·Nash·MMJSUN</t>
+          <t>Jenny</t>
         </is>
       </c>
       <c r="E21" s="36" t="n"/>
       <c r="F21" s="36" t="n"/>
       <c r="G21" s="36" t="n"/>
-      <c r="H21" s="36" t="n"/>
+      <c r="H21" s="45" t="inlineStr">
+        <is>
+          <t>Jenny</t>
+        </is>
+      </c>
       <c r="I21" s="36" t="n"/>
-      <c r="J21" s="36" t="n"/>
-      <c r="K21" s="36" t="n"/>
-      <c r="L21" s="48" t="inlineStr">
-        <is>
-          <t>Bright·Nash·MMJSUN</t>
-        </is>
-      </c>
-      <c r="M21" s="49" t="n"/>
-      <c r="N21" s="49" t="n"/>
-      <c r="O21" s="49" t="n"/>
+      <c r="J21" s="78" t="n"/>
+      <c r="K21" s="46" t="n"/>
+      <c r="L21" s="46" t="n"/>
+      <c r="M21" s="36" t="n"/>
+      <c r="N21" s="36" t="n"/>
+      <c r="O21" s="36" t="n"/>
       <c r="P21" s="36" t="n"/>
       <c r="Q21" s="36" t="n"/>
       <c r="R21" s="36" t="n"/>
@@ -3627,22 +3569,22 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="27" t="inlineStr">
         <is>
-          <t>T18</t>
-        </is>
-      </c>
-      <c r="B22" s="32" t="inlineStr">
-        <is>
-          <t>前端框架初始化 + 首頁（Mock 資料）</t>
-        </is>
-      </c>
-      <c r="C22" s="44" t="inlineStr">
-        <is>
-          <t>前端/UX</t>
+          <t>T19</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>FastAPI 端點實作（讀 DB）</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>地基/架構</t>
         </is>
       </c>
       <c r="D22" s="27" t="inlineStr">
         <is>
-          <t>Jenny</t>
+          <t>Nash·Jenny·Haoche</t>
         </is>
       </c>
       <c r="E22" s="36" t="n"/>
@@ -3650,15 +3592,15 @@
       <c r="G22" s="36" t="n"/>
       <c r="H22" s="36" t="n"/>
       <c r="I22" s="36" t="n"/>
-      <c r="J22" s="45" t="inlineStr">
-        <is>
-          <t>Jenny</t>
-        </is>
-      </c>
-      <c r="K22" s="46" t="n"/>
-      <c r="L22" s="46" t="n"/>
-      <c r="M22" s="36" t="n"/>
-      <c r="N22" s="36" t="n"/>
+      <c r="J22" s="34" t="inlineStr">
+        <is>
+          <t>Nash·Jenny·Haoche</t>
+        </is>
+      </c>
+      <c r="K22" s="36" t="n"/>
+      <c r="L22" s="78" t="n"/>
+      <c r="M22" s="35" t="n"/>
+      <c r="N22" s="35" t="n"/>
       <c r="O22" s="36" t="n"/>
       <c r="P22" s="36" t="n"/>
       <c r="Q22" s="36" t="n"/>
@@ -3668,22 +3610,22 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="27" t="inlineStr">
         <is>
-          <t>T19</t>
-        </is>
-      </c>
-      <c r="B23" s="28" t="inlineStr">
-        <is>
-          <t>FastAPI 端點實作（讀 DB）</t>
-        </is>
-      </c>
-      <c r="C23" s="33" t="inlineStr">
-        <is>
-          <t>地基/架構</t>
+          <t>T20</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>端到端串接（英雄場景：台積電法說）</t>
+        </is>
+      </c>
+      <c r="C23" s="29" t="inlineStr">
+        <is>
+          <t>整合</t>
         </is>
       </c>
       <c r="D23" s="27" t="inlineStr">
         <is>
-          <t>Nash·Jenny·Haoche</t>
+          <t>Nash·Arku·Timyo·MMJSUN·Bright·Haoche</t>
         </is>
       </c>
       <c r="E23" s="36" t="n"/>
@@ -3693,28 +3635,28 @@
       <c r="I23" s="36" t="n"/>
       <c r="J23" s="36" t="n"/>
       <c r="K23" s="36" t="n"/>
-      <c r="L23" s="34" t="inlineStr">
-        <is>
-          <t>Nash·Jenny·Haoche</t>
-        </is>
-      </c>
-      <c r="M23" s="35" t="n"/>
-      <c r="N23" s="35" t="n"/>
-      <c r="O23" s="36" t="n"/>
-      <c r="P23" s="36" t="n"/>
-      <c r="Q23" s="36" t="n"/>
+      <c r="L23" s="55" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
+      <c r="M23" s="36" t="n"/>
+      <c r="N23" s="36" t="n"/>
+      <c r="O23" s="78" t="n"/>
+      <c r="P23" s="31" t="n"/>
+      <c r="Q23" s="31" t="n"/>
       <c r="R23" s="36" t="n"/>
       <c r="S23" s="36" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="27" t="inlineStr">
         <is>
-          <t>T20</t>
-        </is>
-      </c>
-      <c r="B24" s="32" t="inlineStr">
-        <is>
-          <t>端到端串接（英雄場景：台積電法說）</t>
+          <t>T21</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>APScheduler 排程整合（管線每輪 + 每日批次）</t>
         </is>
       </c>
       <c r="C24" s="29" t="inlineStr">
@@ -3724,7 +3666,7 @@
       </c>
       <c r="D24" s="27" t="inlineStr">
         <is>
-          <t>Nash·Arku·Timyo·MMJSUN·Bright·Haoche</t>
+          <t>Arku·Bright</t>
         </is>
       </c>
       <c r="E24" s="36" t="n"/>
@@ -3734,38 +3676,38 @@
       <c r="I24" s="36" t="n"/>
       <c r="J24" s="36" t="n"/>
       <c r="K24" s="36" t="n"/>
-      <c r="L24" s="36" t="n"/>
+      <c r="L24" s="30" t="inlineStr">
+        <is>
+          <t>Arku·Bright</t>
+        </is>
+      </c>
       <c r="M24" s="36" t="n"/>
       <c r="N24" s="36" t="n"/>
-      <c r="O24" s="55" t="inlineStr">
-        <is>
-          <t>全員</t>
-        </is>
-      </c>
+      <c r="O24" s="78" t="n"/>
       <c r="P24" s="31" t="n"/>
       <c r="Q24" s="31" t="n"/>
-      <c r="R24" s="36" t="n"/>
+      <c r="R24" s="31" t="n"/>
       <c r="S24" s="36" t="n"/>
     </row>
     <row r="25" ht="26.25" customHeight="1">
       <c r="A25" s="27" t="inlineStr">
         <is>
-          <t>T21</t>
-        </is>
-      </c>
-      <c r="B25" s="28" t="inlineStr">
-        <is>
-          <t>APScheduler 排程整合（管線每輪 + 每日批次）</t>
-        </is>
-      </c>
-      <c r="C25" s="29" t="inlineStr">
-        <is>
-          <t>整合</t>
+          <t>T22</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>事件詳情頁 + 籌碼拆解 + 搜尋/時間線</t>
+        </is>
+      </c>
+      <c r="C25" s="44" t="inlineStr">
+        <is>
+          <t>前端/UX</t>
         </is>
       </c>
       <c r="D25" s="27" t="inlineStr">
         <is>
-          <t>Arku·Bright</t>
+          <t>Jenny·MMJSUN</t>
         </is>
       </c>
       <c r="E25" s="36" t="n"/>
@@ -3774,39 +3716,39 @@
       <c r="H25" s="36" t="n"/>
       <c r="I25" s="36" t="n"/>
       <c r="J25" s="36" t="n"/>
-      <c r="K25" s="36" t="n"/>
+      <c r="K25" s="45" t="inlineStr">
+        <is>
+          <t>Jenny·MMJSUN</t>
+        </is>
+      </c>
       <c r="L25" s="36" t="n"/>
       <c r="M25" s="36" t="n"/>
       <c r="N25" s="36" t="n"/>
-      <c r="O25" s="30" t="inlineStr">
-        <is>
-          <t>Arku·Bright</t>
-        </is>
-      </c>
-      <c r="P25" s="31" t="n"/>
-      <c r="Q25" s="31" t="n"/>
-      <c r="R25" s="31" t="n"/>
+      <c r="O25" s="78" t="n"/>
+      <c r="P25" s="46" t="n"/>
+      <c r="Q25" s="46" t="n"/>
+      <c r="R25" s="46" t="n"/>
       <c r="S25" s="36" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="27" t="inlineStr">
         <is>
-          <t>T22</t>
+          <t>T23</t>
         </is>
       </c>
       <c r="B26" s="32" t="inlineStr">
         <is>
-          <t>事件詳情頁 + 籌碼拆解 + 搜尋/時間線</t>
-        </is>
-      </c>
-      <c r="C26" s="44" t="inlineStr">
-        <is>
-          <t>前端/UX</t>
+          <t>去重 F1 / 分類準確率 驗證</t>
+        </is>
+      </c>
+      <c r="C26" s="56" t="inlineStr">
+        <is>
+          <t>驗證</t>
         </is>
       </c>
       <c r="D26" s="27" t="inlineStr">
         <is>
-          <t>Jenny·MMJSUN</t>
+          <t>Timyo·MMJSUN</t>
         </is>
       </c>
       <c r="E26" s="36" t="n"/>
@@ -3815,29 +3757,29 @@
       <c r="H26" s="36" t="n"/>
       <c r="I26" s="36" t="n"/>
       <c r="J26" s="36" t="n"/>
-      <c r="K26" s="36" t="n"/>
+      <c r="K26" s="57" t="inlineStr">
+        <is>
+          <t>Timyo·MMJSUN</t>
+        </is>
+      </c>
       <c r="L26" s="36" t="n"/>
       <c r="M26" s="36" t="n"/>
       <c r="N26" s="36" t="n"/>
-      <c r="O26" s="45" t="inlineStr">
-        <is>
-          <t>Jenny·MMJSUN</t>
-        </is>
-      </c>
-      <c r="P26" s="46" t="n"/>
-      <c r="Q26" s="46" t="n"/>
-      <c r="R26" s="46" t="n"/>
+      <c r="O26" s="78" t="n"/>
+      <c r="P26" s="58" t="n"/>
+      <c r="Q26" s="58" t="n"/>
+      <c r="R26" s="36" t="n"/>
       <c r="S26" s="36" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="27" t="inlineStr">
         <is>
-          <t>T23</t>
+          <t>T24</t>
         </is>
       </c>
       <c r="B27" s="32" t="inlineStr">
         <is>
-          <t>去重 F1 / 分類準確率 驗證</t>
+          <t>評分行為合理性驗證（跨天平滑/分歧閘門）</t>
         </is>
       </c>
       <c r="C27" s="56" t="inlineStr">
@@ -3847,7 +3789,7 @@
       </c>
       <c r="D27" s="27" t="inlineStr">
         <is>
-          <t>Timyo·MMJSUN</t>
+          <t>Bright</t>
         </is>
       </c>
       <c r="E27" s="36" t="n"/>
@@ -3856,29 +3798,29 @@
       <c r="H27" s="36" t="n"/>
       <c r="I27" s="36" t="n"/>
       <c r="J27" s="36" t="n"/>
-      <c r="K27" s="36" t="n"/>
+      <c r="K27" s="57" t="inlineStr">
+        <is>
+          <t>Bright</t>
+        </is>
+      </c>
       <c r="L27" s="36" t="n"/>
       <c r="M27" s="36" t="n"/>
       <c r="N27" s="36" t="n"/>
-      <c r="O27" s="57" t="inlineStr">
-        <is>
-          <t>Timyo·MMJSUN</t>
-        </is>
-      </c>
-      <c r="P27" s="58" t="n"/>
+      <c r="O27" s="36" t="n"/>
+      <c r="P27" s="78" t="n"/>
       <c r="Q27" s="58" t="n"/>
-      <c r="R27" s="36" t="n"/>
+      <c r="R27" s="58" t="n"/>
       <c r="S27" s="36" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="27" t="inlineStr">
         <is>
-          <t>T24</t>
+          <t>T25</t>
         </is>
       </c>
       <c r="B28" s="32" t="inlineStr">
         <is>
-          <t>評分行為合理性驗證（跨天平滑/分歧閘門）</t>
+          <t>全套 Docker Compose up 整合測試</t>
         </is>
       </c>
       <c r="C28" s="56" t="inlineStr">
@@ -3888,7 +3830,7 @@
       </c>
       <c r="D28" s="27" t="inlineStr">
         <is>
-          <t>Bright</t>
+          <t>Nash·Arku·Haoche</t>
         </is>
       </c>
       <c r="E28" s="36" t="n"/>
@@ -3899,37 +3841,37 @@
       <c r="J28" s="36" t="n"/>
       <c r="K28" s="36" t="n"/>
       <c r="L28" s="36" t="n"/>
-      <c r="M28" s="36" t="n"/>
+      <c r="M28" s="57" t="inlineStr">
+        <is>
+          <t>Nash·Arku·Haoche</t>
+        </is>
+      </c>
       <c r="N28" s="36" t="n"/>
       <c r="O28" s="36" t="n"/>
-      <c r="P28" s="57" t="inlineStr">
-        <is>
-          <t>Bright</t>
-        </is>
-      </c>
-      <c r="Q28" s="58" t="n"/>
+      <c r="P28" s="36" t="n"/>
+      <c r="Q28" s="78" t="n"/>
       <c r="R28" s="58" t="n"/>
       <c r="S28" s="36" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="27" t="inlineStr">
         <is>
-          <t>T25</t>
-        </is>
-      </c>
-      <c r="B29" s="32" t="inlineStr">
-        <is>
-          <t>全套 Docker Compose up 整合測試</t>
-        </is>
-      </c>
-      <c r="C29" s="56" t="inlineStr">
-        <is>
-          <t>驗證</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>Nash·Arku·Haoche</t>
+          <t>T26</t>
+        </is>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>Demo 準備 + 文件整理</t>
+        </is>
+      </c>
+      <c r="C29" s="59" t="inlineStr">
+        <is>
+          <t>收尾</t>
+        </is>
+      </c>
+      <c r="D29" s="41" t="inlineStr">
+        <is>
+          <t>全員</t>
         </is>
       </c>
       <c r="E29" s="36" t="n"/>
@@ -3942,25 +3884,25 @@
       <c r="L29" s="36" t="n"/>
       <c r="M29" s="36" t="n"/>
       <c r="N29" s="36" t="n"/>
-      <c r="O29" s="36" t="n"/>
+      <c r="O29" s="60" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
       <c r="P29" s="36" t="n"/>
-      <c r="Q29" s="57" t="inlineStr">
-        <is>
-          <t>Nash·Arku·Haoche</t>
-        </is>
-      </c>
-      <c r="R29" s="58" t="n"/>
-      <c r="S29" s="36" t="n"/>
+      <c r="Q29" s="36" t="n"/>
+      <c r="R29" s="78" t="n"/>
+      <c r="S29" s="61" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="27" t="inlineStr">
         <is>
-          <t>T26</t>
-        </is>
-      </c>
-      <c r="B30" s="28" t="inlineStr">
-        <is>
-          <t>Demo 準備 + 文件整理</t>
+          <t>T27</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>緩衝 / Bug 修復</t>
         </is>
       </c>
       <c r="C30" s="59" t="inlineStr">
@@ -3983,57 +3925,17 @@
       <c r="L30" s="36" t="n"/>
       <c r="M30" s="36" t="n"/>
       <c r="N30" s="36" t="n"/>
-      <c r="O30" s="36" t="n"/>
+      <c r="O30" s="60" t="inlineStr">
+        <is>
+          <t>全員</t>
+        </is>
+      </c>
       <c r="P30" s="36" t="n"/>
       <c r="Q30" s="36" t="n"/>
-      <c r="R30" s="60" t="inlineStr">
-        <is>
-          <t>全員</t>
-        </is>
-      </c>
-      <c r="S30" s="61" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="27" t="inlineStr">
-        <is>
-          <t>T27</t>
-        </is>
-      </c>
-      <c r="B31" s="32" t="inlineStr">
-        <is>
-          <t>緩衝 / Bug 修復</t>
-        </is>
-      </c>
-      <c r="C31" s="59" t="inlineStr">
-        <is>
-          <t>收尾</t>
-        </is>
-      </c>
-      <c r="D31" s="41" t="inlineStr">
-        <is>
-          <t>全員</t>
-        </is>
-      </c>
-      <c r="E31" s="36" t="n"/>
-      <c r="F31" s="36" t="n"/>
-      <c r="G31" s="36" t="n"/>
-      <c r="H31" s="36" t="n"/>
-      <c r="I31" s="36" t="n"/>
-      <c r="J31" s="36" t="n"/>
-      <c r="K31" s="36" t="n"/>
-      <c r="L31" s="36" t="n"/>
-      <c r="M31" s="36" t="n"/>
-      <c r="N31" s="36" t="n"/>
-      <c r="O31" s="36" t="n"/>
-      <c r="P31" s="36" t="n"/>
-      <c r="Q31" s="36" t="n"/>
-      <c r="R31" s="36" t="n"/>
-      <c r="S31" s="60" t="inlineStr">
-        <is>
-          <t>全員</t>
-        </is>
-      </c>
-    </row>
+      <c r="R30" s="36" t="n"/>
+      <c r="S30" s="78" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>

--- a/工作分配.xlsx
+++ b/工作分配.xlsx
@@ -391,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -603,6 +603,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1041,7 +1044,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>開發環境 + Docker Compose（db 服務先起）</t>
+          <t>開發環境 + Docker Compose（api/worker；DB 用 Neon 雲端）</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -1074,18 +1077,16 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>docker-compose 能起 db</t>
-        </is>
-      </c>
-      <c r="M5" s="14" t="inlineStr">
+          <t>Compose(api/worker) 起得來 + 能連上 Neon</t>
+        </is>
+      </c>
+      <c r="M5" s="79" t="inlineStr">
         <is>
           <t>• 環境：裝 Docker Desktop，docker compose version 可跑
-• 檔案：寫 docker-compose.yml 的 db 服務，image pgvector/pgvector:pg16
-• 先做：只起 db（compose up -d db），能用 DBeaver/psql 連上就算過
-• 存哪：DB 資料掛 volume，容器重建資料不消失
-• 秘密：DB 密碼放 .env（複製 .env.example），別寫死
-• ★ 這步是全隊地基：你做完別人才連得上資料庫
-• ★ 關鍵節點：完成後與 Haoche 一起驗收再通知下游</t>
+• DB：不起本地 db 容器，改連 Neon 雲端 Postgres——先在 Neon 建專案，連線字串放 .env(DATABASE_URL)，全隊共用同一個庫
+• 檔案：docker-compose.yml 只含 api + worker 兩服務（原 db 那格移除）
+• 先做：能連上 Neon（DBeaver/psql 用連線字串連通）+ api 容器起得來就算過
+• 好處：不用每人各起本地 db、資料共享；排程只在整合/demo 期跑，Neon 免費層 CU-hrs 夠</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1108,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>PostgreSQL + pgvector 建置 + init.sql</t>
+          <t>Neon 建庫 + pgvector + init.sql</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1140,16 +1141,16 @@
       </c>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>可連線的向量資料庫</t>
-        </is>
-      </c>
-      <c r="M6" s="14" t="inlineStr">
-        <is>
-          <t>• 環境：T01 的 db 容器要先起來
-• 檔案：infra_Nash/postgres/init.sql 寫 CREATE EXTENSION vector;
+          <t>Neon 上可連線、pgvector 就緒的向量庫</t>
+        </is>
+      </c>
+      <c r="M6" s="79" t="inlineStr">
+        <is>
+          <t>• 環境：Neon 專案已建、連線字串就緒（T01）
+• 先確認：Neon 的 pgvector 擴充是否支援 vector(1024)（未驗證，動手前查官方）
+• 檔案：infra_Nash/postgres/init.sql 寫 CREATE EXTENSION vector;（在 Neon 上跑）
 • 注意：向量欄位維度 = 1024（BGE-M3）
-• 驗證：能建一張含 vector(1024) 的測試表
-• ★ 關鍵節點：完成後與 Haoche 一起驗收再通知下游</t>
+• 驗證：能在 Neon 建一張含 vector(1024) 的測試表</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1657,7 @@
       <c r="M14" s="10" t="inlineStr">
         <is>
           <t>• ★ 環境：需 db(T01)+events 表(T03)；模型檔放 data/models/（別進 git）
-• 前置：彙整 T07 全員心得
+• BGE-M3 已定案（Timyo dedup.py）；T07 全員實驗已取消
 • 定案：模型 / 維度1024 / 前處理 / 去重閾值 一組寫死
 • 檔案：backend/app/pipeline/embedding_Timyo/bge_m3.py
 • 存哪：讀 articles(pending) → 算向量 → 寫 events.embedding → status=vectorized</t>
@@ -2877,7 +2878,7 @@
       </c>
       <c r="B5" s="32" t="inlineStr">
         <is>
-          <t>開發環境 + Docker Compose（db 服務先起）</t>
+          <t>開發環境 + Docker Compose（api/worker；DB 用 Neon 雲端）</t>
         </is>
       </c>
       <c r="C5" s="33" t="inlineStr">
@@ -2918,7 +2919,7 @@
       </c>
       <c r="B6" s="28" t="inlineStr">
         <is>
-          <t>PostgreSQL + pgvector 建置 + init.sql</t>
+          <t>Neon 建庫 + pgvector + init.sql</t>
         </is>
       </c>
       <c r="C6" s="33" t="inlineStr">
@@ -4005,11 +4006,11 @@
         </is>
       </c>
       <c r="C3" s="65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="28" t="inlineStr">
         <is>
-          <t>T01、T02、T03、T04、T07、T17、T19、T20、T25、T26、T27</t>
+          <t>T01、T02、T03、T04、T17、T19、T20、T25、T26、T27</t>
         </is>
       </c>
     </row>
@@ -4025,11 +4026,11 @@
         </is>
       </c>
       <c r="C4" s="65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="28" t="inlineStr">
         <is>
-          <t>T05、T06、T07、T10、T20、T21、T25、T26、T27</t>
+          <t>T05、T06、T10、T20、T21、T25、T26、T27</t>
         </is>
       </c>
     </row>
@@ -4045,11 +4046,11 @@
         </is>
       </c>
       <c r="C5" s="65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="28" t="inlineStr">
         <is>
-          <t>T01、T07、T11、T12、T20、T23、T26、T27</t>
+          <t>T01、T11、T12、T20、T23、T26、T27</t>
         </is>
       </c>
     </row>
@@ -4065,11 +4066,11 @@
         </is>
       </c>
       <c r="C6" s="65" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="28" t="inlineStr">
         <is>
-          <t>T07、T13、T14、T17、T20、T22、T23、T26、T27</t>
+          <t>T13、T14、T17、T20、T22、T23、T26、T27</t>
         </is>
       </c>
     </row>
@@ -4085,11 +4086,11 @@
         </is>
       </c>
       <c r="C7" s="65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" s="28" t="inlineStr">
         <is>
-          <t>T03、T07、T09、T15、T16、T17、T20、T21、T24、T26、T27</t>
+          <t>T03、T09、T15、T16、T17、T20、T21、T24、T26、T27</t>
         </is>
       </c>
     </row>
@@ -4105,11 +4106,11 @@
         </is>
       </c>
       <c r="C8" s="65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="28" t="inlineStr">
         <is>
-          <t>T04、T06、T07、T08、T18、T19、T20、T22、T26、T27</t>
+          <t>T04、T06、T08、T18、T19、T20、T22、T26、T27</t>
         </is>
       </c>
     </row>
@@ -4125,11 +4126,11 @@
         </is>
       </c>
       <c r="C9" s="65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>T00、T01、T02、T03、T04、T07、T19、T20、T25、T26、T27</t>
+          <t>T00、T01、T02、T03、T04、T19、T20、T25、T26、T27</t>
         </is>
       </c>
     </row>
@@ -4188,14 +4189,14 @@
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="74" t="inlineStr">
         <is>
-          <t>4. 高優先任務配置 2–3 人：地基(T01-04)、Embedding 實驗(T07 全員)、市場驗證(T17 三人)、端到端串接(T20)、收尾(T26 全員)。</t>
+          <t>4. 高優先任務配置 2–3 人：地基(T01-04)、市場驗證(T17 三人)、端到端串接(T20)、收尾(T26 全員)。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="74" t="inlineStr">
         <is>
-          <t>5. 先地基後模組再整合：W1 打通環境/資料流並全員玩 Embedding；W2 核心模組並行；W3 整合、驗證、Demo。契約優先(T04)讓前端可先用 Mock 並行。</t>
+          <t>5. CSV 解耦並行：各模組用冻结樣本(接口=v2 契約)獨立開發、不等 DB，DB 整合集中後段。W1 地基+各線並行、W2 核心模組、W3(壓至 D10) 整合/驗證/串接；T26/27 收尾。契約優先(T04)+Mock 讓前端並行。</t>
         </is>
       </c>
     </row>
